--- a/artfynd/A 23364-2025 artfynd.xlsx
+++ b/artfynd/A 23364-2025 artfynd.xlsx
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125564061</v>
+        <v>125562173</v>
       </c>
       <c r="B5" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,39 +1027,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>603923</v>
+        <v>604077</v>
       </c>
       <c r="R5" t="n">
-        <v>6937238</v>
+        <v>6937189</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,11 +1087,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Purfärska spår. Även äldre spår.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125562173</v>
+        <v>125564928</v>
       </c>
       <c r="B6" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,34 +1129,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>604077</v>
+        <v>604027</v>
       </c>
       <c r="R6" t="n">
-        <v>6937189</v>
+        <v>6937156</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1199,6 +1194,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,7 +1225,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125564928</v>
+        <v>125561890</v>
       </c>
       <c r="B7" t="n">
         <v>57635</v>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>604027</v>
+        <v>604114</v>
       </c>
       <c r="R7" t="n">
-        <v>6937156</v>
+        <v>6937157</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1337,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125561890</v>
+        <v>125562061</v>
       </c>
       <c r="B8" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,39 +1353,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>604114</v>
+        <v>604102</v>
       </c>
       <c r="R8" t="n">
-        <v>6937157</v>
+        <v>6937192</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,11 +1413,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1449,10 +1439,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125562061</v>
+        <v>125564525</v>
       </c>
       <c r="B9" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1465,34 +1455,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>604102</v>
+        <v>603911</v>
       </c>
       <c r="R9" t="n">
-        <v>6937192</v>
+        <v>6937162</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1525,6 +1520,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1551,7 +1551,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125564525</v>
+        <v>125562495</v>
       </c>
       <c r="B10" t="n">
         <v>57635</v>
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>603911</v>
+        <v>604063</v>
       </c>
       <c r="R10" t="n">
-        <v>6937162</v>
+        <v>6937173</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1663,10 +1663,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125562495</v>
+        <v>125562908</v>
       </c>
       <c r="B11" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1679,39 +1679,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>604063</v>
+        <v>604018</v>
       </c>
       <c r="R11" t="n">
-        <v>6937173</v>
+        <v>6937236</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1744,11 +1739,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1775,10 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125562908</v>
+        <v>125564061</v>
       </c>
       <c r="B12" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1791,34 +1781,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>604018</v>
+        <v>603923</v>
       </c>
       <c r="R12" t="n">
-        <v>6937236</v>
+        <v>6937238</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1851,6 +1846,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Purfärska spår. Även äldre spår.</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 23364-2025 artfynd.xlsx
+++ b/artfynd/A 23364-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125564551</v>
+        <v>125564928</v>
       </c>
       <c r="B2" t="n">
         <v>57635</v>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>603914</v>
+        <v>604027</v>
       </c>
       <c r="R2" t="n">
-        <v>6937147</v>
+        <v>6937156</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125564712</v>
+        <v>125562908</v>
       </c>
       <c r="B3" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>603972</v>
+        <v>604018</v>
       </c>
       <c r="R3" t="n">
-        <v>6937162</v>
+        <v>6937236</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,11 +863,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125562759</v>
+        <v>125562704</v>
       </c>
       <c r="B4" t="n">
         <v>57635</v>
@@ -935,7 +925,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1113,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125564928</v>
+        <v>125562061</v>
       </c>
       <c r="B6" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,39 +1119,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>604027</v>
+        <v>604102</v>
       </c>
       <c r="R6" t="n">
-        <v>6937156</v>
+        <v>6937192</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,11 +1179,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125561890</v>
+        <v>125564712</v>
       </c>
       <c r="B7" t="n">
         <v>57635</v>
@@ -1261,7 +1241,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1270,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>604114</v>
+        <v>603972</v>
       </c>
       <c r="R7" t="n">
-        <v>6937157</v>
+        <v>6937162</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1337,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125562061</v>
+        <v>125561890</v>
       </c>
       <c r="B8" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,34 +1333,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>604102</v>
+        <v>604114</v>
       </c>
       <c r="R8" t="n">
-        <v>6937192</v>
+        <v>6937157</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1413,6 +1398,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1551,7 +1541,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125562495</v>
+        <v>125564551</v>
       </c>
       <c r="B10" t="n">
         <v>57635</v>
@@ -1596,10 +1586,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>604063</v>
+        <v>603914</v>
       </c>
       <c r="R10" t="n">
-        <v>6937173</v>
+        <v>6937147</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1663,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125562908</v>
+        <v>125562495</v>
       </c>
       <c r="B11" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1679,34 +1669,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>604018</v>
+        <v>604063</v>
       </c>
       <c r="R11" t="n">
-        <v>6937236</v>
+        <v>6937173</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1739,6 +1734,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 23364-2025 artfynd.xlsx
+++ b/artfynd/A 23364-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125564928</v>
+        <v>125562495</v>
       </c>
       <c r="B2" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -720,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>604027</v>
+        <v>604063</v>
       </c>
       <c r="R2" t="n">
-        <v>6937156</v>
+        <v>6937173</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125562908</v>
+        <v>125562704</v>
       </c>
       <c r="B3" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,34 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>604018</v>
+        <v>604030</v>
       </c>
       <c r="R3" t="n">
-        <v>6937236</v>
+        <v>6937187</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -863,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,15 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125562704</v>
+        <v>125561890</v>
       </c>
       <c r="B4" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,7 +920,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -934,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604030</v>
+        <v>604114</v>
       </c>
       <c r="R4" t="n">
-        <v>6937187</v>
+        <v>6937157</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,15 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125562173</v>
+        <v>125564712</v>
       </c>
       <c r="B5" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,34 +1007,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>604077</v>
+        <v>603972</v>
       </c>
       <c r="R5" t="n">
-        <v>6937189</v>
+        <v>6937162</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1077,6 +1072,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,15 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125562061</v>
+        <v>125564525</v>
       </c>
       <c r="B6" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,34 +1114,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>604102</v>
+        <v>603911</v>
       </c>
       <c r="R6" t="n">
-        <v>6937192</v>
+        <v>6937162</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,6 +1179,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,15 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125564712</v>
+        <v>125564928</v>
       </c>
       <c r="B7" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>603972</v>
+        <v>604027</v>
       </c>
       <c r="R7" t="n">
-        <v>6937162</v>
+        <v>6937156</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,15 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125561890</v>
+        <v>125562908</v>
       </c>
       <c r="B8" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1333,39 +1328,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>604114</v>
+        <v>604018</v>
       </c>
       <c r="R8" t="n">
-        <v>6937157</v>
+        <v>6937236</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,11 +1388,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1429,15 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125564525</v>
+        <v>125562173</v>
       </c>
       <c r="B9" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,39 +1425,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>603911</v>
+        <v>604077</v>
       </c>
       <c r="R9" t="n">
-        <v>6937162</v>
+        <v>6937189</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1510,11 +1485,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1541,15 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125564551</v>
+        <v>125562061</v>
       </c>
       <c r="B10" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,39 +1522,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>603914</v>
+        <v>604102</v>
       </c>
       <c r="R10" t="n">
-        <v>6937147</v>
+        <v>6937192</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1622,11 +1582,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,15 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125562495</v>
+        <v>125564551</v>
       </c>
       <c r="B11" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>604063</v>
+        <v>603914</v>
       </c>
       <c r="R11" t="n">
-        <v>6937173</v>
+        <v>6937147</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1768,12 +1718,7 @@
         <v>125564061</v>
       </c>
       <c r="B12" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 23364-2025 artfynd.xlsx
+++ b/artfynd/A 23364-2025 artfynd.xlsx
@@ -1511,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125562061</v>
+        <v>125564551</v>
       </c>
       <c r="B10" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1522,34 +1522,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>604102</v>
+        <v>603914</v>
       </c>
       <c r="R10" t="n">
-        <v>6937192</v>
+        <v>6937147</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1582,6 +1587,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1608,10 +1618,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125564551</v>
+        <v>125562061</v>
       </c>
       <c r="B11" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1619,39 +1629,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>603914</v>
+        <v>604102</v>
       </c>
       <c r="R11" t="n">
-        <v>6937147</v>
+        <v>6937192</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1684,11 +1689,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 23364-2025 artfynd.xlsx
+++ b/artfynd/A 23364-2025 artfynd.xlsx
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125564712</v>
+        <v>125564525</v>
       </c>
       <c r="B5" t="n">
         <v>57651</v>
@@ -1027,7 +1027,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>603972</v>
+        <v>603911</v>
       </c>
       <c r="R5" t="n">
         <v>6937162</v>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125564525</v>
+        <v>125564712</v>
       </c>
       <c r="B6" t="n">
         <v>57651</v>
@@ -1134,7 +1134,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1143,7 +1143,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>603911</v>
+        <v>603972</v>
       </c>
       <c r="R6" t="n">
         <v>6937162</v>
@@ -1511,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125564551</v>
+        <v>125562061</v>
       </c>
       <c r="B10" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1522,39 +1522,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>603914</v>
+        <v>604102</v>
       </c>
       <c r="R10" t="n">
-        <v>6937147</v>
+        <v>6937192</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1587,11 +1582,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1618,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125562061</v>
+        <v>125564551</v>
       </c>
       <c r="B11" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1629,34 +1619,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>604102</v>
+        <v>603914</v>
       </c>
       <c r="R11" t="n">
-        <v>6937192</v>
+        <v>6937147</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1689,6 +1684,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 23364-2025 artfynd.xlsx
+++ b/artfynd/A 23364-2025 artfynd.xlsx
@@ -1320,7 +1320,7 @@
         <v>125562908</v>
       </c>
       <c r="B8" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>125562173</v>
       </c>
       <c r="B9" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>125562061</v>
       </c>
       <c r="B10" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 23364-2025 artfynd.xlsx
+++ b/artfynd/A 23364-2025 artfynd.xlsx
@@ -1320,7 +1320,7 @@
         <v>125562908</v>
       </c>
       <c r="B8" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>125562173</v>
       </c>
       <c r="B9" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>125562061</v>
       </c>
       <c r="B10" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 23364-2025 artfynd.xlsx
+++ b/artfynd/A 23364-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125562495</v>
       </c>
       <c r="B2" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>125562704</v>
       </c>
       <c r="B3" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>125561890</v>
       </c>
       <c r="B4" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>125564525</v>
       </c>
       <c r="B5" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>125564712</v>
       </c>
       <c r="B6" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>125564928</v>
       </c>
       <c r="B7" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>125562908</v>
       </c>
       <c r="B8" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>125562173</v>
       </c>
       <c r="B9" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>125562061</v>
       </c>
       <c r="B10" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>125564551</v>
       </c>
       <c r="B11" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>125564061</v>
       </c>
       <c r="B12" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 23364-2025 artfynd.xlsx
+++ b/artfynd/A 23364-2025 artfynd.xlsx
@@ -1511,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125562061</v>
+        <v>125564551</v>
       </c>
       <c r="B10" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1522,34 +1522,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>604102</v>
+        <v>603914</v>
       </c>
       <c r="R10" t="n">
-        <v>6937192</v>
+        <v>6937147</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1582,6 +1587,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1608,10 +1618,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125564551</v>
+        <v>125562061</v>
       </c>
       <c r="B11" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1619,39 +1629,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>603914</v>
+        <v>604102</v>
       </c>
       <c r="R11" t="n">
-        <v>6937147</v>
+        <v>6937192</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1684,11 +1689,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 23364-2025 artfynd.xlsx
+++ b/artfynd/A 23364-2025 artfynd.xlsx
@@ -1511,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125564551</v>
+        <v>125562061</v>
       </c>
       <c r="B10" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1522,39 +1522,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>603914</v>
+        <v>604102</v>
       </c>
       <c r="R10" t="n">
-        <v>6937147</v>
+        <v>6937192</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1587,11 +1582,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1618,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125562061</v>
+        <v>125564551</v>
       </c>
       <c r="B11" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1629,34 +1619,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>604102</v>
+        <v>603914</v>
       </c>
       <c r="R11" t="n">
-        <v>6937192</v>
+        <v>6937147</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1689,6 +1684,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 23364-2025 artfynd.xlsx
+++ b/artfynd/A 23364-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125562495</v>
       </c>
       <c r="B2" t="n">
-        <v>57652</v>
+        <v>57736</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>125562704</v>
       </c>
       <c r="B3" t="n">
-        <v>57652</v>
+        <v>57736</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>125561890</v>
       </c>
       <c r="B4" t="n">
-        <v>57652</v>
+        <v>57736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>125564525</v>
       </c>
       <c r="B5" t="n">
-        <v>57652</v>
+        <v>57736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>125564712</v>
       </c>
       <c r="B6" t="n">
-        <v>57652</v>
+        <v>57736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>125564928</v>
       </c>
       <c r="B7" t="n">
-        <v>57652</v>
+        <v>57736</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>125564551</v>
       </c>
       <c r="B10" t="n">
-        <v>57652</v>
+        <v>57736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>125564061</v>
       </c>
       <c r="B12" t="n">
-        <v>57652</v>
+        <v>57736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 23364-2025 artfynd.xlsx
+++ b/artfynd/A 23364-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125562495</v>
       </c>
       <c r="B2" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>125562704</v>
       </c>
       <c r="B3" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>125561890</v>
       </c>
       <c r="B4" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>125564525</v>
       </c>
       <c r="B5" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>125564712</v>
       </c>
       <c r="B6" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>125564928</v>
       </c>
       <c r="B7" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>125564551</v>
       </c>
       <c r="B10" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>125564061</v>
       </c>
       <c r="B12" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 23364-2025 artfynd.xlsx
+++ b/artfynd/A 23364-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125562495</v>
+        <v>125562061</v>
       </c>
       <c r="B2" t="n">
-        <v>57741</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>604063</v>
+        <v>604102</v>
       </c>
       <c r="R2" t="n">
-        <v>6937173</v>
+        <v>6937192</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,50 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125562704</v>
+        <v>125562173</v>
       </c>
       <c r="B3" t="n">
-        <v>57741</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>604030</v>
+        <v>604077</v>
       </c>
       <c r="R3" t="n">
-        <v>6937187</v>
+        <v>6937189</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,50 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125561890</v>
+        <v>125562908</v>
       </c>
       <c r="B4" t="n">
-        <v>57741</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604114</v>
+        <v>604018</v>
       </c>
       <c r="R4" t="n">
-        <v>6937157</v>
+        <v>6937236</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125564525</v>
+        <v>125561890</v>
       </c>
       <c r="B5" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>603911</v>
+        <v>604114</v>
       </c>
       <c r="R5" t="n">
-        <v>6937162</v>
+        <v>6937157</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125564712</v>
+        <v>125562495</v>
       </c>
       <c r="B6" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,7 +1104,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1143,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>603972</v>
+        <v>604063</v>
       </c>
       <c r="R6" t="n">
-        <v>6937162</v>
+        <v>6937173</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125564928</v>
+        <v>125562704</v>
       </c>
       <c r="B7" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,7 +1211,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1250,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>604027</v>
+        <v>604030</v>
       </c>
       <c r="R7" t="n">
-        <v>6937156</v>
+        <v>6937187</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125562908</v>
+        <v>125564061</v>
       </c>
       <c r="B8" t="n">
-        <v>78973</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,34 +1298,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>604018</v>
+        <v>603923</v>
       </c>
       <c r="R8" t="n">
-        <v>6937236</v>
+        <v>6937238</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,6 +1363,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Purfärska spår. Även äldre spår.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125562173</v>
+        <v>125564525</v>
       </c>
       <c r="B9" t="n">
-        <v>78973</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1425,34 +1405,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>604077</v>
+        <v>603911</v>
       </c>
       <c r="R9" t="n">
-        <v>6937189</v>
+        <v>6937162</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1485,6 +1470,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1514,7 +1504,7 @@
         <v>125564551</v>
       </c>
       <c r="B10" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1618,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125562061</v>
+        <v>125564573</v>
       </c>
       <c r="B11" t="n">
-        <v>78973</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1629,34 +1619,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>604102</v>
+        <v>603917</v>
       </c>
       <c r="R11" t="n">
-        <v>6937192</v>
+        <v>6937138</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1689,6 +1684,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1715,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125564061</v>
+        <v>125564712</v>
       </c>
       <c r="B12" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>603923</v>
+        <v>603972</v>
       </c>
       <c r="R12" t="n">
-        <v>6937238</v>
+        <v>6937162</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack på tall. Purfärska spår. Även äldre spår.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1819,6 +1819,220 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>125564928</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lill-Rödmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>604027</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6937156</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Indal</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>125565043</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lill-Rödmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>604005</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6937107</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Indal</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23364-2025 artfynd.xlsx
+++ b/artfynd/A 23364-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125562061</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125562173</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125562908</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125561890</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125562495</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125562704</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1391,6 +1426,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125564061</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1498,6 +1538,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125564525</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1605,6 +1650,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125564551</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1712,6 +1762,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125564573</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1819,6 +1874,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125564712</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1926,6 +1986,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125564928</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2033,8 +2098,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125565043</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>